--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N73_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N73_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.76831757168739</v>
+        <v>6.624851605399201</v>
       </c>
       <c r="D2" t="n">
-        <v>40.98312565576521</v>
+        <v>6.659757919061846</v>
       </c>
       <c r="E2" t="n">
-        <v>12.67634199686863</v>
+        <v>2.059905574491153</v>
       </c>
       <c r="F2" t="n">
-        <v>13.25052187960615</v>
+        <v>2.153209805436</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>56.26520605979631</v>
+        <v>9.143095984716901</v>
       </c>
       <c r="D3" t="n">
-        <v>55.95038852106426</v>
+        <v>9.091938134672942</v>
       </c>
       <c r="E3" t="n">
-        <v>12.67634199686863</v>
+        <v>2.059905574491153</v>
       </c>
       <c r="F3" t="n">
-        <v>13.25052187960615</v>
+        <v>2.153209805436</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.00051314725542</v>
+        <v>3.575083386429005</v>
       </c>
       <c r="D4" t="n">
-        <v>21.43839258707917</v>
+        <v>3.483738795400365</v>
       </c>
       <c r="E4" t="n">
-        <v>12.67634199686863</v>
+        <v>2.059905574491153</v>
       </c>
       <c r="F4" t="n">
-        <v>13.25052187960615</v>
+        <v>2.153209805436</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>63.04248127621531</v>
+        <v>10.24440320738499</v>
       </c>
       <c r="D5" t="n">
-        <v>62.35601744318198</v>
+        <v>10.13285283451707</v>
       </c>
       <c r="E5" t="n">
-        <v>12.67634199686863</v>
+        <v>2.059905574491153</v>
       </c>
       <c r="F5" t="n">
-        <v>13.25052187960615</v>
+        <v>2.153209805436</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.99323224701368</v>
+        <v>5.198900240139723</v>
       </c>
       <c r="D6" t="n">
-        <v>33.45531870055473</v>
+        <v>5.436489288840145</v>
       </c>
       <c r="E6" t="n">
-        <v>12.67634199686863</v>
+        <v>2.059905574491153</v>
       </c>
       <c r="F6" t="n">
-        <v>13.25052187960615</v>
+        <v>2.153209805436</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.28828292167936</v>
+        <v>6.059345974772897</v>
       </c>
       <c r="D7" t="n">
-        <v>33.10966626228661</v>
+        <v>5.380320767621575</v>
       </c>
       <c r="E7" t="n">
-        <v>12.67634199686863</v>
+        <v>2.059905574491153</v>
       </c>
       <c r="F7" t="n">
-        <v>13.25052187960615</v>
+        <v>2.153209805436</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.67770322557666</v>
+        <v>4.985126774156208</v>
       </c>
       <c r="D8" t="n">
-        <v>25.51924254215276</v>
+        <v>4.146876913099824</v>
       </c>
       <c r="E8" t="n">
-        <v>12.67634199686863</v>
+        <v>2.059905574491153</v>
       </c>
       <c r="F8" t="n">
-        <v>13.25052187960615</v>
+        <v>2.153209805436</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.24910786179337</v>
+        <v>7.027980027541423</v>
       </c>
       <c r="D9" t="n">
-        <v>42.71990004617379</v>
+        <v>6.941983757503241</v>
       </c>
       <c r="E9" t="n">
-        <v>12.67634199686863</v>
+        <v>2.059905574491153</v>
       </c>
       <c r="F9" t="n">
-        <v>13.25052187960615</v>
+        <v>2.153209805436</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
